--- a/Result/profitability/6197.xlsx
+++ b/Result/profitability/6197.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.6</v>
       </c>
       <c r="M2" t="n">
-        <v>2.0725</v>
+        <v>2.27375</v>
       </c>
       <c r="N2" t="n">
-        <v>31.9475</v>
+        <v>32.31875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>1.80875</v>
+        <v>2.0425</v>
       </c>
       <c r="N3" t="n">
-        <v>30.11875</v>
+        <v>30.74375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.16</v>
       </c>
       <c r="M4" t="n">
-        <v>1.54875</v>
+        <v>1.81875</v>
       </c>
       <c r="N4" t="n">
-        <v>28.0925</v>
+        <v>28.43375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.51</v>
       </c>
       <c r="M5" t="n">
-        <v>1.28125</v>
+        <v>1.49375</v>
       </c>
       <c r="N5" t="n">
-        <v>26.55375</v>
+        <v>26.74625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.3</v>
       </c>
       <c r="M6" t="n">
-        <v>1.0575</v>
+        <v>1.23375</v>
       </c>
       <c r="N6" t="n">
-        <v>24.59875</v>
+        <v>24.99125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.4</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.9625</v>
       </c>
       <c r="N7" t="n">
-        <v>22.455</v>
+        <v>22.33625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>0.53</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5549999999999999</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>19.89125</v>
+        <v>19.9175</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6197</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2509</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1606</v>
+      </c>
+      <c r="E75" t="n">
+        <v>903</v>
+      </c>
+      <c r="F75" t="n">
+        <v>35.98</v>
+      </c>
+      <c r="G75" t="n">
+        <v>574</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>22.88%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>34</v>
+      </c>
+      <c r="J75" t="n">
+        <v>608</v>
+      </c>
+      <c r="K75" t="n">
+        <v>464</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.47125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>34.15</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.5800000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1806853582554517</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.2099999999999937</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.005870841487279677</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.8133971291866031</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.539999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.04471544715447151</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
